--- a/out/WineBank_資本政策シミュレーション.xlsx
+++ b/out/WineBank_資本政策シミュレーション.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③トランシェ比較" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④2社への割付" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤事前に潰す論点" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥既存株主入替え" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,14 +21,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="¥#,##0;(¥#,##0);-"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="9">
     <font>
-      <name val="Calibri"/>
+      <name val="メイリオ"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -115,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,6 +164,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2038,4 +2048,546 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="2" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>既存株主を入れ替えて強力なパートナーを迎える場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>経営陣以外の株主を買い取り、パートナーが譲受＋増資で持分を取る前提。単位：株／円</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>【1】株主の色分け</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>FD 株数</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>FD 比率</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>経営陣ブロック（残留）</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>4367</v>
+      </c>
+      <c r="D6" s="31">
+        <f>C6/'②希薄化余地'!$C$5</f>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>中野ブロック3,961＋小田垣200＋戸高SO200＋従業員6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち 中野ブロック</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>3961</v>
+      </c>
+      <c r="D7" s="12">
+        <f>C7/'②希薄化余地'!$C$5</f>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>中野個人3,413＋SO170＋Crown Jewel box 287＋スペースバンク91</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>売却対象（外部株主）</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>1423</v>
+      </c>
+      <c r="D8" s="19">
+        <f>C8/'②希薄化余地'!$C$5</f>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>MFV749＋Private BANK375＋ベクトル157＋個人90＋寺田52</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>買取・引受 単価（前提）</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="n">
+        <v>450000</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026年1月ラウンドと同額を仮置き。ここを変えると【2】【3】が再計算されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>【2】売却対象株主の取得原価　※買取交渉の難易度</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>株主</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>株数</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>取得原価 合計</t>
+        </is>
+      </c>
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>取得単価</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>@45万での倍率</t>
+        </is>
+      </c>
+      <c r="G12" s="40" t="inlineStr">
+        <is>
+          <t>受取額 @45万</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>マネーフォワードベンチャーズ</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>749</v>
+      </c>
+      <c r="D13" s="41" t="n">
+        <v>250095000</v>
+      </c>
+      <c r="E13" s="41">
+        <f>D13/C13</f>
+        <v/>
+      </c>
+      <c r="F13" s="42">
+        <f>C13*$C$9/D13</f>
+        <v/>
+      </c>
+      <c r="G13" s="41">
+        <f>C13*$C$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>株式会社Private BANK</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>375</v>
+      </c>
+      <c r="D14" s="41" t="n">
+        <v>18750000</v>
+      </c>
+      <c r="E14" s="41">
+        <f>D14/C14</f>
+        <v/>
+      </c>
+      <c r="F14" s="42">
+        <f>C14*$C$9/D14</f>
+        <v/>
+      </c>
+      <c r="G14" s="41">
+        <f>C14*$C$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>株式会社ベクトル</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>157</v>
+      </c>
+      <c r="D15" s="41" t="n">
+        <v>30144000</v>
+      </c>
+      <c r="E15" s="41">
+        <f>D15/C15</f>
+        <v/>
+      </c>
+      <c r="F15" s="42">
+        <f>C15*$C$9/D15</f>
+        <v/>
+      </c>
+      <c r="G15" s="41">
+        <f>C15*$C$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>個人投資家様</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="D16" s="41" t="n">
+        <v>40500000</v>
+      </c>
+      <c r="E16" s="41">
+        <f>D16/C16</f>
+        <v/>
+      </c>
+      <c r="F16" s="42">
+        <f>C16*$C$9/D16</f>
+        <v/>
+      </c>
+      <c r="G16" s="41">
+        <f>C16*$C$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>寺田倉庫株式会社</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" s="41" t="n">
+        <v>9984000</v>
+      </c>
+      <c r="E17" s="41">
+        <f>D17/C17</f>
+        <v/>
+      </c>
+      <c r="F17" s="42">
+        <f>C17*$C$9/D17</f>
+        <v/>
+      </c>
+      <c r="G17" s="41">
+        <f>C17*$C$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C18" s="14">
+        <f>SUM(C13:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="43">
+        <f>SUM(D13:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="43">
+        <f>SUM(G13:G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>※取得原価の大半が低い株主（Private BANK 9.0倍・ベクトル/寺田 2.3倍）は売却に応じやすい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>※実質的な交渉相手はマネーフォワードベンチャーズ1社。@45万では1.35倍にとどまり、価格を押してくる可能性が高い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>※個人投資家様90株は2026年1月に@45万で参加したばかりで簿価売却となるため、別途の配慮が要る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>【3】パートナー持分別の投下額　※外部1,423株の譲受＋増資</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>パートナー 目標持分</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>必要な増資 株数</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>譲受＋増資の
+投下総額</t>
+        </is>
+      </c>
+      <c r="E25" s="30" t="inlineStr">
+        <is>
+          <t>上場前 総株数</t>
+        </is>
+      </c>
+      <c r="F25" s="30" t="inlineStr">
+        <is>
+          <t>中野ブロック
+比率</t>
+        </is>
+      </c>
+      <c r="G25" s="30" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="28" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="C26" s="11">
+        <f>($B26*'②希薄化余地'!$C$5-$C$8)/(1-$B26)</f>
+        <v/>
+      </c>
+      <c r="D26" s="44">
+        <f>($C$8+C26)*$C$9</f>
+        <v/>
+      </c>
+      <c r="E26" s="11">
+        <f>'②希薄化余地'!$C$5+C26</f>
+        <v/>
+      </c>
+      <c r="F26" s="31">
+        <f>'②希薄化余地'!$C$6/E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>拒否権ライン。持分法適用で相手のPLに乗る</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C27" s="11">
+        <f>($B27*'②希薄化余地'!$C$5-$C$8)/(1-$B27)</f>
+        <v/>
+      </c>
+      <c r="D27" s="44">
+        <f>($C$8+C27)*$C$9</f>
+        <v/>
+      </c>
+      <c r="E27" s="11">
+        <f>'②希薄化余地'!$C$5+C27</f>
+        <v/>
+      </c>
+      <c r="F27" s="31">
+        <f>'②希薄化余地'!$C$6/E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>筆頭株主は中野氏のまま。実質的な共同経営</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="45" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="C28" s="34">
+        <f>($B28*'②希薄化余地'!$C$5-$C$8)/(1-$B28)</f>
+        <v/>
+      </c>
+      <c r="D28" s="35">
+        <f>($C$8+C28)*$C$9</f>
+        <v/>
+      </c>
+      <c r="E28" s="34">
+        <f>'②希薄化余地'!$C$5+C28</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>'②希薄化余地'!$C$6/E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>連結子会社化。上場は親子上場となる</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>※投下総額は@45万換算。支配権プレミアムを乗せれば増え、FY2026の着地を理由に値引きされれば減ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>【4】過半数を渡す場合に必ず起きること</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>親子上場</t>
+        </is>
+      </c>
+      <c r="C33" s="39" t="inlineStr">
+        <is>
+          <t>上場会社が過半数を持つと、WineBankの上場は親子上場になる。東証は支配株主を有する上場会社へのガバナンス要求を強めており、上場審査では親会社からの独立性が厳しく問われる。実務的には、出口はIPOではなく将来の完全子会社化（M&amp;A）に寄る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>赤字の連結</t>
+        </is>
+      </c>
+      <c r="C34" s="39" t="inlineStr">
+        <is>
+          <t>過半数を取った相手はWineBankの損益を全部取り込む。FY2026の経常▲124.8百万円を連結する判断は上場会社にとって重い。プランDの黒字化を確認してからのほうが、相手は動きやすい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>IPOを残す道</t>
+        </is>
+      </c>
+      <c r="C35" s="39" t="inlineStr">
+        <is>
+          <t>パートナーを33.4〜49%にとどめれば親子上場にはならず、持分法で相手のPLには乗る。「本気度」は比率ではなく、独占提携・役員派遣・相手の営業目標への組み込み・未達時のラチェットで担保する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="46" customHeight="1">
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>PEという選択肢</t>
+        </is>
+      </c>
+      <c r="C36" s="39" t="inlineStr">
+        <is>
+          <t>既存株主を全部買い取り、経営改革し、数年でIPOに持っていくのはプライベートエクイティの標準的な仕事。PEが40%前後、事業会社が10〜15%で並走する二階建てなら、株主整理・経営改革・IPOの3つを同時に満たせる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C33:G33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>